--- a/ExcelTool/LubanTools/DataTables/Datas/PcbSlotData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/PcbSlotData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F329C829-63BB-4865-B37C-A93A981E5CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10480" yWindow="1620" windowWidth="26660" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
